--- a/data/Swaza.xlsx
+++ b/data/Swaza.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="822" documentId="8_{8C8FC0BD-0490-4651-93D7-D4F920861B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DC34786-6B15-48A9-A3F4-A8A552110CCE}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="1_{288E13BE-C0AA-4D0A-BC1E-61A9BAE93B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E5AC8E3-A949-4A74-A092-341DE03279D8}"/>
   <bookViews>
-    <workbookView xWindow="6015" yWindow="1995" windowWidth="22320" windowHeight="13170" xr2:uid="{D4854224-B691-4ECE-9B28-8D8426E96185}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D4854224-B691-4ECE-9B28-8D8426E96185}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$2362</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36985,11 +36986,8 @@
   </si>
   <si>
     <t>スリラーバーク　ホグバックの屋敷　風呂場</t>
-    <rPh sb="22" eb="24">
-      <t>ヤシキ</t>
-    </rPh>
-    <rPh sb="25" eb="28">
-      <t>フロバ</t>
+    <rPh sb="0" eb="20">
+      <t>ヤシキフロバ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -36999,10 +36997,7 @@
       <t>ヤシキ</t>
     </rPh>
     <rPh sb="24" eb="27">
-      <t>サイジョウカイ</t>
-    </rPh>
-    <rPh sb="34" eb="37">
-      <t>ケンキュウジョ</t>
+      <t>サイジョウカイケンキュウジョ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -38728,10 +38723,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -58598,7 +58589,7 @@
         <v>734</v>
       </c>
       <c r="B753" s="1" t="s">
-        <v>734</v>
+        <v>22</v>
       </c>
       <c r="C753" s="1">
         <v>401</v>
